--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -8261,7 +8261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9479,51 +9479,51 @@
     </row>
     <row r="54">
       <c r="A54" s="18" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>QoS</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>~/qos_runs</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+        <v>46310</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>测量</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16b</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
@@ -9531,24 +9531,24 @@
       <c r="A56" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -9556,24 +9556,24 @@
       <c r="A57" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -9581,24 +9581,24 @@
       <c r="A58" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -9613,17 +9613,17 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -9631,24 +9631,24 @@
       <c r="A60" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -9656,9 +9656,9 @@
       <c r="A61" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -9681,24 +9681,24 @@
       <c r="A62" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -9706,24 +9706,24 @@
       <c r="A63" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9731,24 +9731,24 @@
       <c r="A64" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="20" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -9756,24 +9756,24 @@
       <c r="A65" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -9788,17 +9788,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9806,24 +9806,24 @@
       <c r="A67" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -9831,24 +9831,24 @@
       <c r="A68" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -9906,24 +9906,24 @@
       <c r="A71" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -9938,17 +9938,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -9958,22 +9958,22 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>开始</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -9981,24 +9981,24 @@
       <c r="A74" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -10006,9 +10006,9 @@
       <c r="A75" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -10018,62 +10018,62 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="18" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="18" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -10088,17 +10088,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10106,24 +10106,24 @@
       <c r="A79" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10156,24 +10156,24 @@
       <c r="A81" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10188,17 +10188,17 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10206,24 +10206,24 @@
       <c r="A83" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10231,24 +10231,24 @@
       <c r="A84" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10256,9 +10256,9 @@
       <c r="A85" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -10268,12 +10268,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10281,24 +10281,24 @@
       <c r="A86" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10306,19 +10306,19 @@
       <c r="A87" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -10338,17 +10338,17 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10356,19 +10356,19 @@
       <c r="A89" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -10381,24 +10381,24 @@
       <c r="A90" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10406,24 +10406,24 @@
       <c r="A91" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -10456,24 +10456,24 @@
       <c r="A93" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10481,9 +10481,9 @@
       <c r="A94" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -10506,24 +10506,24 @@
       <c r="A95" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10531,19 +10531,19 @@
       <c r="A96" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B96" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -10556,20 +10556,24 @@
       <c r="A97" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr"/>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10577,20 +10581,24 @@
       <c r="A98" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="20" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr"/>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10606,12 +10614,12 @@
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10619,24 +10627,20 @@
       <c r="A100" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10649,19 +10653,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10676,12 +10676,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -10751,17 +10751,17 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10769,19 +10769,19 @@
       <c r="A106" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -10794,18 +10794,68 @@
       <c r="A107" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="20" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr"/>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr"/>
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -15,7 +15,7 @@
     <sheet name="历史记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,17 +118,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4DFEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,6 +232,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,9 +247,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2952,7 +2955,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.1 上电到 0° 片亮起 (停转)</a:t>
+              <a:t>KR7.3 连续无故障: 整机实转 (有人值守)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2994,12 +2997,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$294:$A$295</f>
+              <f>'指标趋势'!$A$294</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$294:$B$295</f>
+              <f>'指标趋势'!$B$294</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3119,8 +3122,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46308"/>
+          <max val="46311"/>
+          <min val="46309"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3162,7 +3165,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>s</a:t>
+                  <a:t>h</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3436,7 +3439,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.4 上电到转稳全亮</a:t>
+              <a:t>KR8.1 上电到 0° 片亮起 (停转)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3478,12 +3481,254 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$311</f>
+              <f>'指标趋势'!$A$311:$A$312</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$311</f>
+              <f>'指标趋势'!$B$311:$B$312</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!E310</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$311:$D$312</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$311:$E$312</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G310</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$311:$F$312</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$311:$G$312</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I310</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$311:$H$312</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$311:$I$312</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="46309"/>
+          <min val="46308"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="mm-dd" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>s</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>KR8.4 上电到转稳全亮</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B327</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$328</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$328</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3558,7 +3803,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -3584,7 +3829,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!B327</f>
+              <f>'指标趋势'!B344</f>
             </strRef>
           </tx>
           <spPr>
@@ -3612,12 +3857,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$328:$A$329</f>
+              <f>'指标趋势'!$A$345:$A$346</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$328:$B$329</f>
+              <f>'指标趋势'!$B$345:$B$346</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3627,7 +3872,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!E327</f>
+              <f>'指标趋势'!E344</f>
             </strRef>
           </tx>
           <spPr>
@@ -3648,12 +3893,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$D$328:$D$329</f>
+              <f>'指标趋势'!$D$345:$D$346</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$E$328:$E$329</f>
+              <f>'指标趋势'!$E$345:$E$346</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3663,7 +3908,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!G327</f>
+              <f>'指标趋势'!G344</f>
             </strRef>
           </tx>
           <spPr>
@@ -3684,12 +3929,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$F$328:$F$329</f>
+              <f>'指标趋势'!$F$345:$F$346</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$G$328:$G$329</f>
+              <f>'指标趋势'!$G$345:$G$346</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3699,7 +3944,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!I327</f>
+              <f>'指标趋势'!I344</f>
             </strRef>
           </tx>
           <spPr>
@@ -3720,12 +3965,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$H$328:$H$329</f>
+              <f>'指标趋势'!$H$345:$H$346</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$I$328:$I$329</f>
+              <f>'指标趋势'!$I$345:$I$346</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3800,7 +4045,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -3826,7 +4071,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!B344</f>
+              <f>'指标趋势'!B361</f>
             </strRef>
           </tx>
           <spPr>
@@ -3854,12 +4099,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$345</f>
+              <f>'指标趋势'!$A$362</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$345</f>
+              <f>'指标趋势'!$B$362</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3869,7 +4114,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!E344</f>
+              <f>'指标趋势'!E361</f>
             </strRef>
           </tx>
           <spPr>
@@ -3890,12 +4135,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$D$345:$D$346</f>
+              <f>'指标趋势'!$D$362:$D$363</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$E$345:$E$346</f>
+              <f>'指标趋势'!$E$362:$E$363</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3905,7 +4150,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!G344</f>
+              <f>'指标趋势'!G361</f>
             </strRef>
           </tx>
           <spPr>
@@ -3926,12 +4171,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$F$345:$F$346</f>
+              <f>'指标趋势'!$F$362:$F$363</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$G$345:$G$346</f>
+              <f>'指标趋势'!$G$362:$G$363</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3941,7 +4186,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!I344</f>
+              <f>'指标趋势'!I361</f>
             </strRef>
           </tx>
           <spPr>
@@ -3962,12 +4207,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$H$345:$H$346</f>
+              <f>'指标趋势'!$H$362:$H$363</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$I$345:$I$346</f>
+              <f>'指标趋势'!$I$362:$I$363</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4042,7 +4287,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4055,248 +4300,6 @@
             </a:pPr>
             <a:r>
               <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <scatterChart>
-        <scatterStyle val="lineMarker"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!B361</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="2E75B6"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$362:$A$363</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$B$362:$B$363</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!E361</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="70AD47"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$D$362:$D$363</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$E$362:$E$363</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!G361</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$F$362:$F$363</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$G$362:$G$363</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!I361</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$H$362:$H$363</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$I$362:$I$363</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="20"/>
-      </scatterChart>
-      <valAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46308"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>日期</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="mm-dd" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="20"/>
-      </valAx>
-      <valAx>
-        <axId val="20"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>是/否</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="span"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4538,7 +4541,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.1 可实时播放内容数</a:t>
+              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4580,12 +4583,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$396</f>
+              <f>'指标趋势'!$A$396:$A$397</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$396</f>
+              <f>'指标趋势'!$B$396:$B$397</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4595,7 +4598,249 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!C395</f>
+              <f>'指标趋势'!E395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$396:$D$397</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$396:$E$397</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$396:$F$397</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$396:$G$397</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$396:$H$397</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$396:$I$397</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="46309"/>
+          <min val="46308"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="mm-dd" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>是/否</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>KR10.1 可实时播放内容数</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B412</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$413</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$413</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!C412</f>
             </strRef>
           </tx>
           <spPr>
@@ -4623,12 +4868,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$396</f>
+              <f>'指标趋势'!$A$413</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$396</f>
+              <f>'指标趋势'!$C$413</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4638,7 +4883,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!E395</f>
+              <f>'指标趋势'!E412</f>
             </strRef>
           </tx>
           <spPr>
@@ -4659,12 +4904,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$D$396:$D$397</f>
+              <f>'指标趋势'!$D$413:$D$414</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$E$396:$E$397</f>
+              <f>'指标趋势'!$E$413:$E$414</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4674,7 +4919,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!G395</f>
+              <f>'指标趋势'!G412</f>
             </strRef>
           </tx>
           <spPr>
@@ -4695,12 +4940,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$F$396:$F$397</f>
+              <f>'指标趋势'!$F$413:$F$414</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$G$396:$G$397</f>
+              <f>'指标趋势'!$G$413:$G$414</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4710,7 +4955,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!I395</f>
+              <f>'指标趋势'!I412</f>
             </strRef>
           </tx>
           <spPr>
@@ -4731,12 +4976,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$H$396:$H$397</f>
+              <f>'指标趋势'!$H$413:$H$414</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$I$396:$I$397</f>
+              <f>'指标趋势'!$I$413:$I$414</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4811,7 +5056,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4837,7 +5082,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!B412</f>
+              <f>'指标趋势'!B429</f>
             </strRef>
           </tx>
           <spPr>
@@ -4865,12 +5110,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$413</f>
+              <f>'指标趋势'!$A$430</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$413</f>
+              <f>'指标趋势'!$B$430</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4880,7 +5125,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!C412</f>
+              <f>'指标趋势'!C429</f>
             </strRef>
           </tx>
           <spPr>
@@ -4908,12 +5153,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$413</f>
+              <f>'指标趋势'!$A$430</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$413</f>
+              <f>'指标趋势'!$C$430</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4923,7 +5168,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!E412</f>
+              <f>'指标趋势'!E429</f>
             </strRef>
           </tx>
           <spPr>
@@ -4944,12 +5189,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$D$413:$D$414</f>
+              <f>'指标趋势'!$D$430:$D$431</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$E$413:$E$414</f>
+              <f>'指标趋势'!$E$430:$E$431</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4959,7 +5204,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!G412</f>
+              <f>'指标趋势'!G429</f>
             </strRef>
           </tx>
           <spPr>
@@ -4980,12 +5225,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$F$413:$F$414</f>
+              <f>'指标趋势'!$F$430:$F$431</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$G$413:$G$414</f>
+              <f>'指标趋势'!$G$430:$G$431</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4995,7 +5240,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!I412</f>
+              <f>'指标趋势'!I429</f>
             </strRef>
           </tx>
           <spPr>
@@ -5016,12 +5261,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$H$413:$H$414</f>
+              <f>'指标趋势'!$H$430:$H$431</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$I$413:$I$414</f>
+              <f>'指标趋势'!$I$430:$I$431</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5096,7 +5341,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -5285,7 +5530,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -7915,6 +8160,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>427</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="26" name="Chart 26"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId26"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8261,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8332,16 +8599,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>35/37</t>
+          <t>36/37</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 23/25 + 交付 12/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 24/25 + 交付 12/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8364,16 +8631,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>32/45</t>
+          <t>33/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 15/24 + 交付 17/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 16/24 + 交付 17/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8396,16 +8663,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.6122448979591837</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>30/49</t>
+          <t>31/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 13/24 + 交付 17/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 14/24 + 交付 17/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -8426,13 +8693,13 @@
         <v>46310</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.9459</v>
+        <v>0.973</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0.7111</v>
+        <v>0.7333</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.6122</v>
+        <v>0.6327</v>
       </c>
     </row>
     <row r="8">
@@ -8523,71 +8790,71 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>KR7.3</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>新出现</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>连续无故障: 整机实转 (有人值守) (h, 越大越好)</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>(无) → 1</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>1 / 1 / 1；progress/realspin_v0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>阶段出口清单 — V0 出口  (已打勾 8/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>①2047 PL 切片上板通过</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>D2 (1/1)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -8597,12 +8864,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>②主机实时推流 15 fps</t>
+          <t>①2047 PL 切片上板通过</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>D1 (1/1)</t>
+          <t>D2 (1/1)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -8614,7 +8881,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -8624,12 +8891,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>③几何更正 + 镜像已核实</t>
+          <t>②主机实时推流 15 fps</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>KR5.2 (1/1)</t>
+          <t>D1 (1/1)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -8641,7 +8908,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -8651,12 +8918,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
+          <t>③几何更正 + 镜像已核实</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>KR8.1;KR8.2;D13 (3/3)</t>
+          <t>KR5.2 (1/1)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -8668,7 +8935,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -8678,12 +8945,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
+          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>D7;KR9.1;KR9.2 (3/3)</t>
+          <t>KR8.1;KR8.2;D13 (3/3)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -8695,7 +8962,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -8705,12 +8972,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>⑥软件链路无人值守 ≥8 h</t>
+          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>KR7.2 (1/1)</t>
+          <t>D7;KR9.1;KR9.2 (3/3)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -8722,7 +8989,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -8732,12 +8999,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+          <t>⑥软件链路无人值守 ≥8 h</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>D15 (1/1)</t>
+          <t>KR7.2 (1/1)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -8749,110 +9016,110 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>D15 (1/1)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>⑧内容 ≥2 + 一种交互</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>KR10.1;KR10.2 (2/2)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>阶段出口清单 — V1 回板当天就绪  (已打勾 4/11；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>D10 (0/1)</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>②桥 1 期 6 链 24 Hz 位流</t>
+          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>D5 (1/1)</t>
+          <t>D10 (0/1)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -8864,7 +9131,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -8874,12 +9141,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>③桥接收 + 1.2G PRBS 测试件</t>
+          <t>②桥 1 期 6 链 24 Hz 位流</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>D4 (1/1)</t>
+          <t>D5 (1/1)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -8891,7 +9158,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -8901,12 +9168,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>④1 期几何 LUT + 校准工具</t>
+          <t>③桥接收 + 1.2G PRBS 测试件</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>D6 (1/1)</t>
+          <t>D4 (1/1)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -8918,22 +9185,22 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
+          <t>④1 期几何 LUT + 校准工具</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>D8 (0/1)</t>
+          <t>D6 (1/1)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -8945,22 +9212,22 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>⑥全链路系统仿真</t>
+          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>D9 (0/1)</t>
+          <t>D8 (0/1)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -8972,22 +9239,22 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>⑦C1 台架逐像素 0 错</t>
+          <t>⑥全链路系统仿真</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>D11 (0/1)</t>
+          <t>D9 (0/1)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -8999,22 +9266,22 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>⑧整机回板点亮步骤 + 一键脚本</t>
+          <t>⑦C1 台架逐像素 0 错</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D11 (0/1)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -9026,17 +9293,17 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+          <t>⑧整机回板点亮步骤 + 一键脚本</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -9053,17 +9320,17 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>⑩面板映射 4 项信息到位</t>
+          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -9080,1782 +9347,1934 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>⑩面板映射 4 项信息到位</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>⑪无串口运维可用</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>D7 (1/1)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>风险表 (risks.csv；红 = 开，黄 = 监控，绿 = 关)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>影响 / 应对</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>负责 · 登记日期 · 来源</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>1.2G 可能过不了</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
 应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>影响：时钟偏差会丢帧
 应对：退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E42" s="19" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>影响：每块下半屏黑
 应对：硬件确认并补 0Ω</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>2260 从未收到合法 ACK（疑物理通路）</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>影响：1 期显示可能起不来
 应对：验证板一颗一组针对此问题，回板验证</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>影响：2 期 32 bit 像素带宽不够
 应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>WiFi/主机负载造成延迟尾巴（10-13 晚 p99 334 ms）</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>影响：延迟抖动超标
 应对：演示时停重任务；后续增量帧</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>影响：高速下接触不良/脱落
 应对：T2 板留 eMMC、打胶</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>D 盘 EIO（IP-guard 驱动）</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>影响：构建/提交偶发失败
 应对：看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>1 期面板映射缺 4 项信息</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>影响：1 期桥表无法定稿
 应对：问硬件同事</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>每日流水 (daily_log.csv，按天倒序)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="18" t="n">
+    <row r="54">
+      <c r="A54" s="20" t="n">
         <v>46310</v>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>KR7.2</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>8 h 无人值守长跑 9/9 通过 (重开轮 23:45-07:45; 判读 S1 行数口径误判已改为覆盖时长 fe53bde); V0 出口 ⑥ 达成 → V0 出口 8/8</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>progress/soak_v0/report.md</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="18" t="n">
+    <row r="55">
+      <c r="A55" s="20" t="n">
         <v>46310</v>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>测量</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>QoS</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>QoS (XMON DDR_S2 QOS_CONFIG=0x0F) 带载对照 (纯切片 30 Hz): 体素流+TCP 迟到 4.12% → 0.000%, CPU memcpy 300 MB/s 91.5% → 0.000%; 2047 32 bit@16.15 rps 完成率无改善 (86/71% vs 无 QoS 91/82%, 带宽上限); 测后寄存器已写回 0</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>~/qos_runs</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="18" t="n">
+    <row r="56">
+      <c r="A56" s="20" t="n">
         <v>46310</v>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>测量</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>D16b</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>4x4 分块上板 A/B: 体素流+TCP 迟到 现布局 5.34%/4.45% (漂移 0.89 pp) vs 分块 4.79%, 收益在漂移内 = 无效; 迟到角度随相位漂移, 非几何换行主导。按约定不合主线, 分支 task/d16b-tile 保留</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d16b-tile 7936b7e</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="18" t="n">
+    <row r="57">
+      <c r="A57" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>用户定 V0/V1/V2 兼容 300-1200 rpm; 实转 583 rpm PL 只 8 fps (等整圈换帧) → D19 半圈换帧开做 (RTL+voxslice+假转扫速验收)</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>用户 10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>用户定流畅显示为一等要求 (V0/V1/V2); D20 阶段 1 流畅度指标+门槛+基线开做 (与 D19 并行)</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>用户 10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>V1/V2</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>转速 300-1200 rpm 纸面预算: 300 rpm 体刷新仅 10 Hz (物理闪烁); V1 358 片只到 ~718 rpm, 1200 需降到 215 片; V2 605 片到 ~1060 rpm; 公共切片核需支持运行时换每圈片数 (见 budget/rpm_range_2026-10-15.md)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>budget/rpm_range_2026-10-15.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>KR7.3</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>实转 1 h 无故障通过 (583 rpm, QoS 开机默认已上卡 7d301a6); V0 必须项全部达成</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>progress/realspin_v0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>实转换帧仅 10.45/s (583 rpm 整圈换帧限制), 用户感觉卡; D19 半圈换帧 + D20 流畅度门槛处理</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>progress/realspin_v0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="18" t="n">
+    <row r="63">
+      <c r="A63" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="18" t="n">
+    <row r="64">
+      <c r="A64" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B64" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="18" t="n">
+    <row r="65">
+      <c r="A65" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B65" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="18" t="n">
+    <row r="66">
+      <c r="A66" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B66" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="18" t="n">
+    <row r="67">
+      <c r="A67" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="18" t="n">
+    <row r="68">
+      <c r="A68" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="18" t="n">
+    <row r="69">
+      <c r="A69" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="18" t="n">
+    <row r="70">
+      <c r="A70" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="18" t="n">
+    <row r="71">
+      <c r="A71" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B65" s="19" t="inlineStr">
+      <c r="B71" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="18" t="n">
+    <row r="72">
+      <c r="A72" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="18" t="n">
+    <row r="73">
+      <c r="A73" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="18" t="n">
+    <row r="74">
+      <c r="A74" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>用户在场实转</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="18" t="n">
+    <row r="75">
+      <c r="A75" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B69" s="19" t="inlineStr">
+      <c r="B75" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>用户 10-14</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="18" t="n">
+    <row r="76">
+      <c r="A76" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="18" t="n">
+    <row r="77">
+      <c r="A77" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B71" s="19" t="inlineStr">
+      <c r="B77" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>用户 10-14</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="18" t="n">
+    <row r="78">
+      <c r="A78" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="18" t="n">
+    <row r="79">
+      <c r="A79" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>根因</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>D15b</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="18" t="n">
+    <row r="80">
+      <c r="A80" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B80" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>D15</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="18" t="n">
+    <row r="81">
+      <c r="A81" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>开始</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>KR7.2</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="18" t="n">
+    <row r="82">
+      <c r="A82" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B76" s="19" t="inlineStr">
+      <c r="B82" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>用户 10-14</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="18" t="n">
+    <row r="83">
+      <c r="A83" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B83" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>KR7.2</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="18" t="n">
+    <row r="84">
+      <c r="A84" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="18" t="n">
+    <row r="85">
+      <c r="A85" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="14" t="inlineStr">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>E7</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="18" t="n">
+    <row r="86">
+      <c r="A86" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B86" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="18" t="n">
+    <row r="87">
+      <c r="A87" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B87" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="18" t="n">
+    <row r="88">
+      <c r="A88" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="14" t="inlineStr">
+      <c r="B88" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="18" t="n">
+    <row r="89">
+      <c r="A89" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="18" t="n">
+    <row r="90">
+      <c r="A90" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="18" t="n">
+    <row r="91">
+      <c r="A91" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="14" t="inlineStr">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="18" t="n">
+    <row r="92">
+      <c r="A92" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B92" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="18" t="n">
+    <row r="93">
+      <c r="A93" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B93" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="18" t="n">
+    <row r="94">
+      <c r="A94" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="18" t="n">
+    <row r="95">
+      <c r="A95" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="18" t="n">
+    <row r="96">
+      <c r="A96" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="14" t="inlineStr">
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>D14</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="18" t="n">
+    <row r="97">
+      <c r="A97" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="18" t="n">
+    <row r="98">
+      <c r="A98" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="18" t="n">
+    <row r="99">
+      <c r="A99" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B99" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="18" t="n">
+    <row r="100">
+      <c r="A100" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="18" t="n">
+    <row r="101">
+      <c r="A101" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B101" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="18" t="n">
+    <row r="102">
+      <c r="A102" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B96" s="16" t="inlineStr">
+      <c r="B102" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="18" t="n">
+    <row r="103">
+      <c r="A103" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B103" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>D15</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="18" t="n">
+    <row r="104">
+      <c r="A104" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="19" t="inlineStr">
+      <c r="B104" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>D3;D4;D5</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="18" t="n">
+    <row r="105">
+      <c r="A105" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="19" t="inlineStr">
+      <c r="B105" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="18" t="n">
+    <row r="106">
+      <c r="A106" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="20" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr"/>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr"/>
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="18" t="n">
+    <row r="107">
+      <c r="A107" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="19" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr"/>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="18" t="n">
+    <row r="108">
+      <c r="A108" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="19" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="18" t="n">
+    <row r="109">
+      <c r="A109" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="19" t="inlineStr">
+      <c r="B109" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="18" t="n">
+    <row r="110">
+      <c r="A110" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B104" s="19" t="inlineStr">
+      <c r="B110" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>D12;D13;D14</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E110" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="18" t="n">
+    <row r="111">
+      <c r="A111" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="B111" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="18" t="n">
+    <row r="112">
+      <c r="A112" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="19" t="inlineStr">
+      <c r="B112" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>D15;D16</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D112" s="7" t="inlineStr">
         <is>
           <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="18" t="n">
+    <row r="113">
+      <c r="A113" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="19" t="inlineStr">
+      <c r="B113" s="21" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>KR5.2</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="18" t="n">
+    <row r="114">
+      <c r="A114" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="16" t="inlineStr">
+      <c r="B114" s="18" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="18" t="n">
+    <row r="115">
+      <c r="A115" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B109" s="20" t="inlineStr">
+      <c r="B115" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr"/>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr"/>
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -10896,7 +11315,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>POV3D 显性目的进度看板 — 2026-10-15  (当前期 V0；状态按「最新硬件实测 vs 当前期目标」自动判定，krs.csv 人工状态列可覆盖)</t>
         </is>
@@ -11031,7 +11450,7 @@
       <c r="I4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -11058,15 +11477,15 @@
           <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>KR1.2</t>
@@ -11090,7 +11509,7 @@
       <c r="I5" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -11117,15 +11536,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q5" s="22" t="n">
+      <c r="Q5" s="23" t="n">
         <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>KR1.7</t>
@@ -11149,7 +11568,7 @@
       <c r="I6" s="6" t="n">
         <v>236.6</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -11176,15 +11595,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="n">
+      <c r="Q6" s="23" t="n">
         <v>0.5071851225697379</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>KR1.3</t>
@@ -11208,7 +11627,7 @@
       <c r="I7" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -11235,15 +11654,15 @@
           <t>claude_memory/project_m90_wifi_p2p_1012.md</t>
         </is>
       </c>
-      <c r="Q7" s="22" t="n">
+      <c r="Q7" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n"/>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>KR1.4</t>
@@ -11267,7 +11686,7 @@
       <c r="I8" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -11294,15 +11713,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q8" s="22" t="n">
+      <c r="Q8" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n"/>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>KR1.5</t>
@@ -11326,7 +11745,7 @@
       <c r="I9" s="6" t="n">
         <v>17.3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -11349,13 +11768,13 @@
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="n"/>
+      <c r="Q9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="24" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>KR1.6</t>
@@ -11379,7 +11798,7 @@
       <c r="I10" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -11406,7 +11825,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
         </is>
       </c>
-      <c r="Q10" s="22" t="n">
+      <c r="Q10" s="23" t="n">
         <v>0.7200000000000001</v>
       </c>
     </row>
@@ -11452,7 +11871,7 @@
       <c r="I11" s="6" t="n">
         <v>21.7</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -11479,7 +11898,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q11" s="22" t="n">
+      <c r="Q11" s="23" t="n">
         <v>0.7233333333333333</v>
       </c>
     </row>
@@ -11525,7 +11944,7 @@
       <c r="I12" s="6" t="n">
         <v>28800</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -11552,15 +11971,15 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="n">
+      <c r="Q12" s="23" t="n">
         <v>0.6944444444444444</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>KR3.2</t>
@@ -11584,7 +12003,7 @@
       <c r="I13" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -11611,7 +12030,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q13" s="22" t="n">
+      <c r="Q13" s="23" t="n">
         <v>0.2347107438016529</v>
       </c>
     </row>
@@ -11629,7 +12048,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>⏸ 无数据 / 未开始</t>
         </is>
@@ -11657,7 +12076,7 @@
       <c r="I14" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -11684,15 +12103,15 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q14" s="22" t="n">
+      <c r="Q14" s="23" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n"/>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
+      <c r="A15" s="25" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>KR4.2</t>
@@ -11716,7 +12135,7 @@
       <c r="I15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -11733,7 +12152,7 @@
       <c r="N15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="25" t="inlineStr">
+      <c r="O15" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -11743,7 +12162,7 @@
           <t>dr1v90 1995be8 (D15 阶段 1, 主会话复验)</t>
         </is>
       </c>
-      <c r="Q15" s="22" t="n">
+      <c r="Q15" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11789,7 +12208,7 @@
       <c r="I16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -11816,15 +12235,15 @@
           <t>dr1v90 44ed2cd</t>
         </is>
       </c>
-      <c r="Q16" s="22" t="n">
+      <c r="Q16" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
           <t>KR5.2</t>
@@ -11848,7 +12267,7 @@
       <c r="I17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -11875,7 +12294,7 @@
           <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
         </is>
       </c>
-      <c r="Q17" s="22" t="n">
+      <c r="Q17" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11921,7 +12340,7 @@
       <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -11948,7 +12367,7 @@
           <t>dr1v90 3bc5736</t>
         </is>
       </c>
-      <c r="Q18" s="22" t="n">
+      <c r="Q18" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11966,9 +12385,9 @@
           <t>稳定</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>⏸ 无数据 / 未开始</t>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -11994,7 +12413,7 @@
       <c r="I19" s="6" t="n">
         <v>0.0012</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="20" t="n">
         <v>46310</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -12021,15 +12440,15 @@
           <t>dr1v90 fe53bde</t>
         </is>
       </c>
-      <c r="Q19" s="22" t="n">
+      <c r="Q19" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n"/>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>KR7.2</t>
@@ -12053,7 +12472,7 @@
       <c r="I20" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="20" t="n">
         <v>46310</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -12080,15 +12499,15 @@
           <t>dr1v90 fe53bde; progress/soak_v0/report.md</t>
         </is>
       </c>
-      <c r="Q20" s="22" t="n">
+      <c r="Q20" s="23" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>KR7.3</t>
@@ -12109,9 +12528,17 @@
           <t>越大越好</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="7" t="inlineStr"/>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="n">
         <v>1</v>
       </c>
@@ -12121,13 +12548,19 @@
       <c r="N21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="25" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>progress/realspin_v0/</t>
+        </is>
+      </c>
+      <c r="Q21" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -12143,7 +12576,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -12171,7 +12604,7 @@
       <c r="I22" s="6" t="n">
         <v>12.4</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -12198,15 +12631,15 @@
           <t>dr1v90 d13_boot/runs/20261014_145507 (串口 3 次)</t>
         </is>
       </c>
-      <c r="Q22" s="22" t="n">
+      <c r="Q22" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="n"/>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
           <t>KR8.4</t>
@@ -12230,7 +12663,7 @@
       <c r="I23" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -12241,7 +12674,7 @@
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="16" t="inlineStr">
+      <c r="O23" s="18" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12251,13 +12684,13 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q23" s="22" t="n"/>
+      <c r="Q23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="n"/>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>KR8.2</t>
@@ -12281,7 +12714,7 @@
       <c r="I24" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J24" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -12308,15 +12741,15 @@
           <t>dr1v90 d13_boot/runs/20261014_145507</t>
         </is>
       </c>
-      <c r="Q24" s="22" t="n">
+      <c r="Q24" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="n"/>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="24" t="n"/>
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>KR8.3</t>
@@ -12340,7 +12773,7 @@
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -12367,7 +12800,7 @@
           <t>dr1v90 30d82f9</t>
         </is>
       </c>
-      <c r="Q25" s="22" t="n">
+      <c r="Q25" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12413,7 +12846,7 @@
       <c r="I26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -12440,15 +12873,15 @@
           <t>dr1v90 dee9be6</t>
         </is>
       </c>
-      <c r="Q26" s="22" t="n">
+      <c r="Q26" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="n"/>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="24" t="n"/>
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>KR9.2</t>
@@ -12472,7 +12905,7 @@
       <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="18" t="n">
+      <c r="J27" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -12499,7 +12932,7 @@
           <t>dr1v90 dee9be6</t>
         </is>
       </c>
-      <c r="Q27" s="22" t="n">
+      <c r="Q27" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12545,7 +12978,7 @@
       <c r="I28" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="J28" s="18" t="n">
+      <c r="J28" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -12572,15 +13005,15 @@
           <t>dr1v90 task/d14-content ffbfeeb + 用户实转观看</t>
         </is>
       </c>
-      <c r="Q28" s="22" t="n">
+      <c r="Q28" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>KR10.2</t>
@@ -12604,7 +13037,7 @@
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -12631,12 +13064,12 @@
           <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
-      <c r="Q29" s="22" t="n">
+      <c r="Q29" s="23" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
@@ -12648,31 +13081,31 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>达成当前期目标</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>进行中 / 未达标</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>无数据 / 未开始</t>
         </is>
@@ -12684,7 +13117,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>退步 / 阻塞</t>
         </is>
@@ -12736,7 +13169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I414"/>
+  <dimension ref="A1:I431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12756,54 +13189,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>KR1.1 内容刷新率 (假转, 管线能力) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12918,54 +13351,54 @@
       <c r="C12" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>KR1.2 端到端延迟 p50 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13019,54 +13452,54 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>KR1.7 端到端延迟抖动 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G38" s="29" t="inlineStr">
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H38" s="29" t="inlineStr">
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I38" s="29" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13120,54 +13553,54 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>KR1.3 WiFi 可用带宽 (Mbit/s, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C55" s="29" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E55" s="29" t="inlineStr">
+      <c r="E55" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F55" s="29" t="inlineStr">
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G55" s="29" t="inlineStr">
+      <c r="G55" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H55" s="29" t="inlineStr">
+      <c r="H55" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I55" s="29" t="inlineStr">
+      <c r="I55" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13255,54 +13688,54 @@
       <c r="C60" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="28" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>KR1.4 主机出帧耗时 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C72" s="29" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D72" s="29" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E72" s="29" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F72" s="29" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G72" s="29" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H72" s="29" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I72" s="29" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13363,34 +13796,34 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="28" t="inlineStr">
+      <c r="A88" s="29" t="inlineStr">
         <is>
           <t>KR1.5 板上切片耗时 (每帧) (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D89" s="29" t="inlineStr">
+      <c r="D89" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E89" s="29" t="inlineStr">
+      <c r="E89" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
@@ -13427,54 +13860,54 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="28" t="inlineStr">
+      <c r="A105" s="29" t="inlineStr">
         <is>
           <t>KR1.6 内容刷新率 (实转上屏) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29" t="inlineStr">
+      <c r="A106" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B106" s="29" t="inlineStr">
+      <c r="B106" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C106" s="29" t="inlineStr">
+      <c r="C106" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D106" s="29" t="inlineStr">
+      <c r="D106" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E106" s="29" t="inlineStr">
+      <c r="E106" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F106" s="29" t="inlineStr">
+      <c r="F106" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G106" s="29" t="inlineStr">
+      <c r="G106" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H106" s="29" t="inlineStr">
+      <c r="H106" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I106" s="29" t="inlineStr">
+      <c r="I106" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13528,54 +13961,54 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="28" t="inlineStr">
+      <c r="A122" s="29" t="inlineStr">
         <is>
           <t>KR2.1 体帧率 (Hz, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="29" t="inlineStr">
+      <c r="A123" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B123" s="29" t="inlineStr">
+      <c r="B123" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C123" s="29" t="inlineStr">
+      <c r="C123" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D123" s="29" t="inlineStr">
+      <c r="D123" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E123" s="29" t="inlineStr">
+      <c r="E123" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F123" s="29" t="inlineStr">
+      <c r="F123" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G123" s="29" t="inlineStr">
+      <c r="G123" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H123" s="29" t="inlineStr">
+      <c r="H123" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I123" s="29" t="inlineStr">
+      <c r="I123" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13645,54 +14078,54 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="28" t="inlineStr">
+      <c r="A139" s="29" t="inlineStr">
         <is>
           <t>KR3.1 每面像素数 (px, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="29" t="inlineStr">
+      <c r="A140" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B140" s="29" t="inlineStr">
+      <c r="B140" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C140" s="29" t="inlineStr">
+      <c r="C140" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D140" s="29" t="inlineStr">
+      <c r="D140" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E140" s="29" t="inlineStr">
+      <c r="E140" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F140" s="29" t="inlineStr">
+      <c r="F140" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G140" s="29" t="inlineStr">
+      <c r="G140" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H140" s="29" t="inlineStr">
+      <c r="H140" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I140" s="29" t="inlineStr">
+      <c r="I140" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13753,54 +14186,54 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="28" t="inlineStr">
+      <c r="A156" s="29" t="inlineStr">
         <is>
           <t>KR3.2 每圈片数 (片, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="29" t="inlineStr">
+      <c r="A157" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B157" s="29" t="inlineStr">
+      <c r="B157" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C157" s="29" t="inlineStr">
+      <c r="C157" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D157" s="29" t="inlineStr">
+      <c r="D157" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E157" s="29" t="inlineStr">
+      <c r="E157" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F157" s="29" t="inlineStr">
+      <c r="F157" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G157" s="29" t="inlineStr">
+      <c r="G157" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H157" s="29" t="inlineStr">
+      <c r="H157" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I157" s="29" t="inlineStr">
+      <c r="I157" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13879,54 +14312,54 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="28" t="inlineStr">
+      <c r="A173" s="29" t="inlineStr">
         <is>
           <t>KR4.1 色深 (bit/通道, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="29" t="inlineStr">
+      <c r="A174" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B174" s="29" t="inlineStr">
+      <c r="B174" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C174" s="29" t="inlineStr">
+      <c r="C174" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D174" s="29" t="inlineStr">
+      <c r="D174" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E174" s="29" t="inlineStr">
+      <c r="E174" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F174" s="29" t="inlineStr">
+      <c r="F174" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G174" s="29" t="inlineStr">
+      <c r="G174" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H174" s="29" t="inlineStr">
+      <c r="H174" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I174" s="29" t="inlineStr">
+      <c r="I174" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14014,54 +14447,54 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="28" t="inlineStr">
+      <c r="A190" s="29" t="inlineStr">
         <is>
           <t>KR4.2 链路色深 12-bit 已验证 (1=是) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="29" t="inlineStr">
+      <c r="A191" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B191" s="29" t="inlineStr">
+      <c r="B191" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C191" s="29" t="inlineStr">
+      <c r="C191" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D191" s="29" t="inlineStr">
+      <c r="D191" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E191" s="29" t="inlineStr">
+      <c r="E191" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F191" s="29" t="inlineStr">
+      <c r="F191" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G191" s="29" t="inlineStr">
+      <c r="G191" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H191" s="29" t="inlineStr">
+      <c r="H191" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I191" s="29" t="inlineStr">
+      <c r="I191" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14115,54 +14548,54 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="28" t="inlineStr">
+      <c r="A207" s="29" t="inlineStr">
         <is>
           <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="29" t="inlineStr">
+      <c r="A208" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B208" s="29" t="inlineStr">
+      <c r="B208" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C208" s="29" t="inlineStr">
+      <c r="C208" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D208" s="29" t="inlineStr">
+      <c r="D208" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E208" s="29" t="inlineStr">
+      <c r="E208" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F208" s="29" t="inlineStr">
+      <c r="F208" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G208" s="29" t="inlineStr">
+      <c r="G208" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H208" s="29" t="inlineStr">
+      <c r="H208" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I208" s="29" t="inlineStr">
+      <c r="I208" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14223,54 +14656,54 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="28" t="inlineStr">
+      <c r="A224" s="29" t="inlineStr">
         <is>
           <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="29" t="inlineStr">
+      <c r="A225" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B225" s="29" t="inlineStr">
+      <c r="B225" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C225" s="29" t="inlineStr">
+      <c r="C225" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D225" s="29" t="inlineStr">
+      <c r="D225" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E225" s="29" t="inlineStr">
+      <c r="E225" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F225" s="29" t="inlineStr">
+      <c r="F225" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G225" s="29" t="inlineStr">
+      <c r="G225" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H225" s="29" t="inlineStr">
+      <c r="H225" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I225" s="29" t="inlineStr">
+      <c r="I225" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14324,54 +14757,54 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="28" t="inlineStr">
+      <c r="A241" s="29" t="inlineStr">
         <is>
           <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="29" t="inlineStr">
+      <c r="A242" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B242" s="29" t="inlineStr">
+      <c r="B242" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C242" s="29" t="inlineStr">
+      <c r="C242" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D242" s="29" t="inlineStr">
+      <c r="D242" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E242" s="29" t="inlineStr">
+      <c r="E242" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F242" s="29" t="inlineStr">
+      <c r="F242" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G242" s="29" t="inlineStr">
+      <c r="G242" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H242" s="29" t="inlineStr">
+      <c r="H242" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I242" s="29" t="inlineStr">
+      <c r="I242" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14425,54 +14858,54 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="28" t="inlineStr">
+      <c r="A258" s="29" t="inlineStr">
         <is>
           <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="29" t="inlineStr">
+      <c r="A259" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B259" s="29" t="inlineStr">
+      <c r="B259" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C259" s="29" t="inlineStr">
+      <c r="C259" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D259" s="29" t="inlineStr">
+      <c r="D259" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E259" s="29" t="inlineStr">
+      <c r="E259" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F259" s="29" t="inlineStr">
+      <c r="F259" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G259" s="29" t="inlineStr">
+      <c r="G259" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H259" s="29" t="inlineStr">
+      <c r="H259" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I259" s="29" t="inlineStr">
+      <c r="I259" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14544,54 +14977,54 @@
       <c r="C262" s="6" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="28" t="inlineStr">
+      <c r="A275" s="29" t="inlineStr">
         <is>
           <t>KR7.2 连续无故障: 软件链路 (假转, 无人值守) (h, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="29" t="inlineStr">
+      <c r="A276" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B276" s="29" t="inlineStr">
+      <c r="B276" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C276" s="29" t="inlineStr">
+      <c r="C276" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D276" s="29" t="inlineStr">
+      <c r="D276" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E276" s="29" t="inlineStr">
+      <c r="E276" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F276" s="29" t="inlineStr">
+      <c r="F276" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G276" s="29" t="inlineStr">
+      <c r="G276" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H276" s="29" t="inlineStr">
+      <c r="H276" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I276" s="29" t="inlineStr">
+      <c r="I276" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14670,54 +15103,54 @@
       <c r="C280" s="6" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="28" t="inlineStr">
-        <is>
-          <t>KR8.1 上电到 0° 片亮起 (停转) (s, 越小越好)</t>
+      <c r="A292" s="29" t="inlineStr">
+        <is>
+          <t>KR7.3 连续无故障: 整机实转 (有人值守) (h, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="29" t="inlineStr">
+      <c r="A293" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B293" s="29" t="inlineStr">
+      <c r="B293" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C293" s="29" t="inlineStr">
+      <c r="C293" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D293" s="29" t="inlineStr">
+      <c r="D293" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E293" s="29" t="inlineStr">
+      <c r="E293" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F293" s="29" t="inlineStr">
+      <c r="F293" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G293" s="29" t="inlineStr">
+      <c r="G293" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H293" s="29" t="inlineStr">
+      <c r="H293" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I293" s="29" t="inlineStr">
+      <c r="I293" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14725,248 +15158,241 @@
     </row>
     <row r="294">
       <c r="A294" s="8" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B294" s="6" t="n">
-        <v>15.8</v>
+        <v>1</v>
       </c>
       <c r="C294" s="6" t="n"/>
       <c r="D294" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E294" s="6" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="F294" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G294" s="6" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="H294" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I294" s="6" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B295" s="6" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="C295" s="6" t="n"/>
       <c r="D295" s="8" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E295" s="6" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="F295" s="8" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="G295" s="6" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="H295" s="8" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="I295" s="6" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="28" t="inlineStr">
-        <is>
-          <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
+      <c r="A309" s="29" t="inlineStr">
+        <is>
+          <t>KR8.1 上电到 0° 片亮起 (停转) (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="29" t="inlineStr">
+      <c r="A310" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B310" s="29" t="inlineStr">
+      <c r="B310" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C310" s="29" t="inlineStr">
+      <c r="C310" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
+        </is>
+      </c>
+      <c r="D310" s="30" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E310" s="30" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F310" s="30" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G310" s="30" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H310" s="30" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I310" s="30" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B311" s="6" t="n">
-        <v>26</v>
+        <v>15.8</v>
       </c>
       <c r="C311" s="6" t="n"/>
+      <c r="D311" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E311" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F311" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G311" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H311" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I311" s="6" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B312" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C312" s="6" t="n"/>
+      <c r="D312" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E312" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F312" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G312" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H312" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I312" s="6" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="326">
-      <c r="A326" s="28" t="inlineStr">
-        <is>
-          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
+      <c r="A326" s="29" t="inlineStr">
+        <is>
+          <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="29" t="inlineStr">
+      <c r="A327" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B327" s="29" t="inlineStr">
+      <c r="B327" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C327" s="29" t="inlineStr">
+      <c r="C327" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
-        </is>
-      </c>
-      <c r="D327" s="29" t="inlineStr">
-        <is>
-          <t>V0 目标 日期</t>
-        </is>
-      </c>
-      <c r="E327" s="29" t="inlineStr">
-        <is>
-          <t>V0 目标</t>
-        </is>
-      </c>
-      <c r="F327" s="29" t="inlineStr">
-        <is>
-          <t>V1 目标 日期</t>
-        </is>
-      </c>
-      <c r="G327" s="29" t="inlineStr">
-        <is>
-          <t>V1 目标</t>
-        </is>
-      </c>
-      <c r="H327" s="29" t="inlineStr">
-        <is>
-          <t>V2 目标 日期</t>
-        </is>
-      </c>
-      <c r="I327" s="29" t="inlineStr">
-        <is>
-          <t>V2 目标</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="8" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B328" s="6" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="C328" s="6" t="n"/>
-      <c r="D328" s="8" t="n">
-        <v>46308</v>
-      </c>
-      <c r="E328" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F328" s="8" t="n">
-        <v>46308</v>
-      </c>
-      <c r="G328" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="H328" s="8" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I328" s="6" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B329" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="C329" s="6" t="n"/>
-      <c r="D329" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E329" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F329" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G329" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="H329" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I329" s="6" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="343">
-      <c r="A343" s="28" t="inlineStr">
-        <is>
-          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
+      <c r="A343" s="29" t="inlineStr">
+        <is>
+          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="29" t="inlineStr">
+      <c r="A344" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B344" s="29" t="inlineStr">
+      <c r="B344" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C344" s="29" t="inlineStr">
+      <c r="C344" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D344" s="29" t="inlineStr">
+      <c r="D344" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E344" s="29" t="inlineStr">
+      <c r="E344" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F344" s="29" t="inlineStr">
+      <c r="F344" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G344" s="29" t="inlineStr">
+      <c r="G344" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H344" s="29" t="inlineStr">
+      <c r="H344" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I344" s="29" t="inlineStr">
+      <c r="I344" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14974,100 +15400,107 @@
     </row>
     <row r="345">
       <c r="A345" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B345" s="6" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="C345" s="6" t="n"/>
       <c r="D345" s="8" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="E345" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F345" s="8" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="G345" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H345" s="8" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="I345" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="346">
+      <c r="A346" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B346" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C346" s="6" t="n"/>
       <c r="D346" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E346" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F346" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G346" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H346" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I346" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="28" t="inlineStr">
-        <is>
-          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
+      <c r="A360" s="29" t="inlineStr">
+        <is>
+          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="29" t="inlineStr">
+      <c r="A361" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B361" s="29" t="inlineStr">
+      <c r="B361" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C361" s="29" t="inlineStr">
+      <c r="C361" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D361" s="29" t="inlineStr">
+      <c r="D361" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E361" s="29" t="inlineStr">
+      <c r="E361" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F361" s="29" t="inlineStr">
+      <c r="F361" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G361" s="29" t="inlineStr">
+      <c r="G361" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H361" s="29" t="inlineStr">
+      <c r="H361" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I361" s="29" t="inlineStr">
+      <c r="I361" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -15075,107 +15508,100 @@
     </row>
     <row r="362">
       <c r="A362" s="8" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B362" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C362" s="6" t="n"/>
       <c r="D362" s="8" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E362" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" s="8" t="n">
+        <v>46306</v>
+      </c>
+      <c r="G362" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" s="8" t="n">
+        <v>46306</v>
+      </c>
+      <c r="I362" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="D363" s="8" t="n">
         <v>46308</v>
       </c>
-      <c r="E362" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F362" s="8" t="n">
+      <c r="E363" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F363" s="8" t="n">
         <v>46308</v>
       </c>
-      <c r="G362" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H362" s="8" t="n">
+      <c r="G363" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" s="8" t="n">
         <v>46308</v>
       </c>
-      <c r="I362" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B363" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C363" s="6" t="n"/>
-      <c r="D363" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E363" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F363" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G363" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H363" s="8" t="n">
-        <v>46309</v>
-      </c>
       <c r="I363" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="28" t="inlineStr">
-        <is>
-          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
+      <c r="A377" s="29" t="inlineStr">
+        <is>
+          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="29" t="inlineStr">
+      <c r="A378" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B378" s="29" t="inlineStr">
+      <c r="B378" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C378" s="29" t="inlineStr">
+      <c r="C378" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D378" s="29" t="inlineStr">
+      <c r="D378" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E378" s="29" t="inlineStr">
+      <c r="E378" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F378" s="29" t="inlineStr">
+      <c r="F378" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G378" s="29" t="inlineStr">
+      <c r="G378" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H378" s="29" t="inlineStr">
+      <c r="H378" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I378" s="29" t="inlineStr">
+      <c r="I378" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -15236,54 +15662,54 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="28" t="inlineStr">
-        <is>
-          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
+      <c r="A394" s="29" t="inlineStr">
+        <is>
+          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="29" t="inlineStr">
+      <c r="A395" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B395" s="29" t="inlineStr">
+      <c r="B395" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C395" s="29" t="inlineStr">
+      <c r="C395" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D395" s="29" t="inlineStr">
+      <c r="D395" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E395" s="29" t="inlineStr">
+      <c r="E395" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F395" s="29" t="inlineStr">
+      <c r="F395" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G395" s="29" t="inlineStr">
+      <c r="G395" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H395" s="29" t="inlineStr">
+      <c r="H395" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I395" s="29" t="inlineStr">
+      <c r="I395" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -15294,99 +15720,104 @@
         <v>46308</v>
       </c>
       <c r="B396" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C396" s="6" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C396" s="6" t="n"/>
       <c r="D396" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E396" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F396" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G396" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H396" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I396" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
+      <c r="A397" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B397" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C397" s="6" t="n"/>
       <c r="D397" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="E397" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F397" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="G397" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H397" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="I397" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="28" t="inlineStr">
-        <is>
-          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+      <c r="A411" s="29" t="inlineStr">
+        <is>
+          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="29" t="inlineStr">
+      <c r="A412" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B412" s="29" t="inlineStr">
+      <c r="B412" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C412" s="29" t="inlineStr">
+      <c r="C412" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D412" s="29" t="inlineStr">
+      <c r="D412" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E412" s="29" t="inlineStr">
+      <c r="E412" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F412" s="29" t="inlineStr">
+      <c r="F412" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G412" s="29" t="inlineStr">
+      <c r="G412" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H412" s="29" t="inlineStr">
+      <c r="H412" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I412" s="29" t="inlineStr">
+      <c r="I412" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -15397,28 +15828,28 @@
         <v>46308</v>
       </c>
       <c r="B413" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C413" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D413" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="E413" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F413" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="G413" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H413" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="I413" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="414">
@@ -15426,18 +15857,121 @@
         <v>46309</v>
       </c>
       <c r="E414" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F414" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="G414" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H414" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="I414" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="29" t="inlineStr">
+        <is>
+          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="30" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B429" s="30" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+      <c r="C429" s="30" t="inlineStr">
+        <is>
+          <t>仿真/台架</t>
+        </is>
+      </c>
+      <c r="D429" s="30" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E429" s="30" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F429" s="30" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G429" s="30" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H429" s="30" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I429" s="30" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B430" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C430" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D430" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E430" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F430" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G430" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H430" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I430" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="D431" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E431" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F431" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G431" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H431" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I431" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15726,10 +16260,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="20" t="n">
         <v>46307</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -15764,10 +16298,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="20" t="n">
         <v>46307</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -15802,10 +16336,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="20" t="n">
         <v>46307</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -15840,10 +16374,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="20" t="n">
         <v>46307</v>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -15878,10 +16412,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="20" t="n">
         <v>46307</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F29" s="20" t="n">
         <v>46307</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -15916,10 +16450,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F30" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -15954,10 +16488,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -15992,10 +16526,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="F32" s="18" t="n">
+      <c r="F32" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -16030,10 +16564,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F33" s="18" t="n">
+      <c r="F33" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -16068,10 +16602,10 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -16106,10 +16640,10 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -16144,10 +16678,10 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -16182,10 +16716,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="20" t="n">
         <v>46310</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="20" t="n">
         <v>46308</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -16220,10 +16754,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -16258,11 +16792,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E39" s="18" t="n">
+      <c r="E39" s="20" t="n">
         <v>46315</v>
       </c>
-      <c r="F39" s="18" t="n"/>
-      <c r="G39" s="25" t="inlineStr">
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16294,11 +16828,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E40" s="18" t="n">
+      <c r="E40" s="20" t="n">
         <v>46317</v>
       </c>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="25" t="inlineStr">
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16330,11 +16864,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="20" t="n">
         <v>46317</v>
       </c>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="25" t="inlineStr">
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16366,11 +16900,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="20" t="n">
         <v>46319</v>
       </c>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="25" t="inlineStr">
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16402,11 +16936,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="20" t="n">
         <v>46310</v>
       </c>
-      <c r="F43" s="18" t="n"/>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16438,10 +16972,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="E44" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="F44" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -16476,11 +17010,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F45" s="18" t="n"/>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="F45" s="20" t="n"/>
+      <c r="G45" s="18" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16512,10 +17046,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -16550,11 +17084,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="F47" s="20" t="n"/>
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16586,9 +17120,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="25" t="inlineStr">
+      <c r="E48" s="20" t="n"/>
+      <c r="F48" s="20" t="n"/>
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16620,9 +17154,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="25" t="inlineStr">
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16654,9 +17188,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="25" t="inlineStr">
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="20" t="n"/>
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16688,9 +17222,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E51" s="18" t="n"/>
-      <c r="F51" s="18" t="n"/>
-      <c r="G51" s="25" t="inlineStr">
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16722,10 +17256,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="F52" s="20" t="n">
         <v>46309</v>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -16814,48 +17348,48 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="20" t="n">
         <v>46317</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="20" t="n">
         <v>46319</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="20" t="n">
         <v>46336</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="20" t="n">
         <v>46338</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="20" t="n">
         <v>46343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>对角线 (y = x)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="31" t="n">
         <v>46308</v>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="31" t="n">
         <v>46308</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="31" t="n">
         <v>46343</v>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="31" t="n">
         <v>46343</v>
       </c>
     </row>
@@ -16871,7 +17405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16933,7 +17467,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
+      <c r="A2" s="31" t="n">
         <v>46157</v>
       </c>
       <c r="B2" s="7" t="n">
@@ -16974,7 +17508,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="31" t="n">
         <v>46157</v>
       </c>
       <c r="B3" s="7" t="n">
@@ -17015,7 +17549,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B4" s="7" t="n">
@@ -17056,7 +17590,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B5" s="7" t="n">
@@ -17097,7 +17631,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B6" s="7" t="n">
@@ -17138,7 +17672,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="31" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="7" t="n">
@@ -17179,7 +17713,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="31" t="n">
         <v>46238</v>
       </c>
       <c r="B8" s="7" t="n">
@@ -17220,7 +17754,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="31" t="n">
         <v>46238</v>
       </c>
       <c r="B9" s="7" t="n">
@@ -17261,7 +17795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="31" t="n">
         <v>46239</v>
       </c>
       <c r="B10" s="7" t="n">
@@ -17302,7 +17836,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="31" t="n">
         <v>46240</v>
       </c>
       <c r="B11" s="7" t="n">
@@ -17343,7 +17877,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="31" t="n">
         <v>46254</v>
       </c>
       <c r="B12" s="7" t="n">
@@ -17384,7 +17918,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="31" t="n">
         <v>46259</v>
       </c>
       <c r="B13" s="7" t="n">
@@ -17425,7 +17959,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="31" t="n">
         <v>46260</v>
       </c>
       <c r="B14" s="7" t="n">
@@ -17466,7 +18000,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="31" t="n">
         <v>46267</v>
       </c>
       <c r="B15" s="7" t="n">
@@ -17507,7 +18041,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="31" t="n">
         <v>46279</v>
       </c>
       <c r="B16" s="7" t="n">
@@ -17548,7 +18082,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="31" t="n">
         <v>46280</v>
       </c>
       <c r="B17" s="7" t="n">
@@ -17589,7 +18123,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="31" t="n">
         <v>46280</v>
       </c>
       <c r="B18" s="7" t="n">
@@ -17630,7 +18164,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B19" s="7" t="n">
@@ -17671,7 +18205,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B20" s="7" t="n">
@@ -17712,7 +18246,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B21" s="7" t="n">
@@ -17753,7 +18287,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B22" s="7" t="n">
@@ -17794,7 +18328,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B23" s="7" t="n">
@@ -17835,7 +18369,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B24" s="7" t="n">
@@ -17876,7 +18410,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B25" s="7" t="n">
@@ -17917,7 +18451,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B26" s="7" t="n">
@@ -17958,7 +18492,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B27" s="7" t="n">
@@ -17999,7 +18533,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B28" s="7" t="n">
@@ -18040,7 +18574,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B29" s="7" t="n">
@@ -18081,7 +18615,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B30" s="7" t="n">
@@ -18122,7 +18656,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B31" s="7" t="n">
@@ -18163,7 +18697,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B32" s="7" t="n">
@@ -18204,7 +18738,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B33" s="7" t="n">
@@ -18245,7 +18779,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B34" s="7" t="n">
@@ -18286,7 +18820,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B35" s="7" t="n">
@@ -18327,7 +18861,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B36" s="7" t="n">
@@ -18368,7 +18902,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B37" s="7" t="n">
@@ -18409,7 +18943,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B38" s="7" t="n">
@@ -18450,7 +18984,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B39" s="7" t="n">
@@ -18491,7 +19025,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B40" s="7" t="n">
@@ -18532,7 +19066,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B41" s="7" t="n">
@@ -18573,7 +19107,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B42" s="7" t="n">
@@ -18614,7 +19148,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B43" s="7" t="n">
@@ -18655,7 +19189,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B44" s="7" t="n">
@@ -18696,7 +19230,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B45" s="7" t="n">
@@ -18737,7 +19271,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B46" s="7" t="n">
@@ -18778,7 +19312,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B47" s="7" t="n">
@@ -18819,7 +19353,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B48" s="7" t="n">
@@ -18860,7 +19394,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B49" s="7" t="n">
@@ -18901,7 +19435,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B50" s="7" t="n">
@@ -18942,7 +19476,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="n">
+      <c r="A51" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B51" s="7" t="n">
@@ -18983,7 +19517,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="n">
+      <c r="A52" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B52" s="7" t="n">
@@ -19024,7 +19558,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="n">
+      <c r="A53" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B53" s="7" t="n">
@@ -19065,7 +19599,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="n">
+      <c r="A54" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B54" s="7" t="n">
@@ -19106,7 +19640,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B55" s="7" t="n">
@@ -19147,7 +19681,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="n">
+      <c r="A56" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B56" s="7" t="n">
@@ -19188,7 +19722,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="n">
+      <c r="A57" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B57" s="7" t="n">
@@ -19229,7 +19763,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="n">
+      <c r="A58" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B58" s="7" t="n">
@@ -19270,7 +19804,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="n">
+      <c r="A59" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B59" s="7" t="n">
@@ -19311,7 +19845,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="n">
+      <c r="A60" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B60" s="7" t="n">
@@ -19352,7 +19886,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="n">
+      <c r="A61" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B61" s="7" t="n">
@@ -19393,7 +19927,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="n">
+      <c r="A62" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B62" s="7" t="n">
@@ -19434,7 +19968,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="n">
+      <c r="A63" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B63" s="7" t="n">
@@ -19475,7 +20009,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="n">
+      <c r="A64" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B64" s="7" t="n">
@@ -19516,7 +20050,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="n">
+      <c r="A65" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B65" s="7" t="n">
@@ -19557,7 +20091,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="n">
+      <c r="A66" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B66" s="7" t="n">
@@ -19598,7 +20132,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="n">
+      <c r="A67" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B67" s="7" t="n">
@@ -19639,7 +20173,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="n">
+      <c r="A68" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B68" s="7" t="n">
@@ -19680,7 +20214,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="n">
+      <c r="A69" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B69" s="7" t="n">
@@ -19721,7 +20255,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="n">
+      <c r="A70" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B70" s="7" t="n">
@@ -19762,7 +20296,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="n">
+      <c r="A71" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B71" s="7" t="n">
@@ -19803,7 +20337,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="n">
+      <c r="A72" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B72" s="7" t="n">
@@ -19844,7 +20378,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="n">
+      <c r="A73" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B73" s="7" t="n">
@@ -19885,7 +20419,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="n">
+      <c r="A74" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B74" s="7" t="n">
@@ -19926,7 +20460,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="n">
+      <c r="A75" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B75" s="7" t="n">
@@ -19967,7 +20501,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="n">
+      <c r="A76" s="31" t="n">
         <v>46309</v>
       </c>
       <c r="B76" s="7" t="n">
@@ -20008,7 +20542,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="n">
+      <c r="A77" s="31" t="n">
         <v>46310</v>
       </c>
       <c r="B77" s="7" t="n">
@@ -20049,7 +20583,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="n">
+      <c r="A78" s="31" t="n">
         <v>46310</v>
       </c>
       <c r="B78" s="7" t="n">
@@ -20089,8 +20623,49 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>KR7.3</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>连续无故障: 整机实转 (有人值守)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>progress/realspin_v0/</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>实转 583 rpm 1 h (有人值守, 开机默认 PL + QoS 开): 停摆 0 / 死 0 / NAK 0 / ERR 0 / 转动 57/57 min / ping 121 丢 0 / 完成率最低 99.84% (16 位回绕已补); 换帧 10.45/s 受转速限制 (D19 在修)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -16079,7 +16079,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -17087,15 +17087,17 @@
       <c r="E47" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="F47" s="20" t="n"/>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F47" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>539d303: 根因 = 按角度 DDR 换行 + 负载叠加; 4×4 分块待用户定</t>
+          <t>QoS 开机默认合主线 7d301a6 (带载迟到 4.1%→0, memcpy 91.5%→0); 4x4 分块 A/B 无收益未合 (task/d16b-tile 保留)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -8528,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9948,51 +9948,51 @@
     </row>
     <row r="62">
       <c r="A62" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>流畅度阶段 1: host/smooth_report.py + 门槛 (软件损失≤3%, 间隔 p99≤2T0, 长停顿≤5‰, 撕裂 0 等, SPEC §12) + voxslice --flip-log; 基线: 8 h 假转软件损失 2.3% 但约每 2 min 一次 2-3 s 无新帧 (主机/链路侧, 板端 PL 无缺口) 判 FAIL; 实转 648 rpm 软件损失 3.5%, 每分钟至少一顿 0.3-1.1 s 判 FAIL。主会话复验中</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d20-smooth 83a5fd7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+        <v>46310</v>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>更多内容 + 手机网页控制合主线 (用户实转看过); 新克隆回归全过</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 e215176</t>
         </is>
       </c>
     </row>
@@ -10000,24 +10000,24 @@
       <c r="A64" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -10025,24 +10025,24 @@
       <c r="A65" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B65" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -10050,24 +10050,24 @@
       <c r="A66" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B66" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10082,17 +10082,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10100,24 +10100,24 @@
       <c r="A68" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B68" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -10125,9 +10125,9 @@
       <c r="A69" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -10150,24 +10150,24 @@
       <c r="A70" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -10175,24 +10175,24 @@
       <c r="A71" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B71" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10200,24 +10200,24 @@
       <c r="A72" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -10225,24 +10225,24 @@
       <c r="A73" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B73" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -10257,17 +10257,17 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10275,24 +10275,24 @@
       <c r="A75" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B75" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -10300,24 +10300,24 @@
       <c r="A76" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -10332,12 +10332,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -10357,17 +10357,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -10375,24 +10375,24 @@
       <c r="A79" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B79" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10407,17 +10407,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -10427,22 +10427,22 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>开始</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -10450,24 +10450,24 @@
       <c r="A82" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -10475,9 +10475,9 @@
       <c r="A83" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B83" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -10487,62 +10487,62 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -10557,17 +10557,17 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10575,24 +10575,24 @@
       <c r="A87" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -10612,12 +10612,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10625,24 +10625,24 @@
       <c r="A89" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10657,17 +10657,17 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10675,24 +10675,24 @@
       <c r="A91" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10700,24 +10700,24 @@
       <c r="A92" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B92" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10725,9 +10725,9 @@
       <c r="A93" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10750,24 +10750,24 @@
       <c r="A94" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10775,19 +10775,19 @@
       <c r="A95" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -10807,17 +10807,17 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10825,19 +10825,19 @@
       <c r="A97" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -10850,24 +10850,24 @@
       <c r="A98" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10875,24 +10875,24 @@
       <c r="A99" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10907,12 +10907,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -10925,24 +10925,24 @@
       <c r="A101" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10950,9 +10950,9 @@
       <c r="A102" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -10975,24 +10975,24 @@
       <c r="A103" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -11000,19 +11000,19 @@
       <c r="A104" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B104" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -11025,20 +11025,24 @@
       <c r="A105" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B105" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr"/>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -11046,20 +11050,24 @@
       <c r="A106" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr"/>
+      <c r="B106" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11083,12 @@
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11088,24 +11096,20 @@
       <c r="A108" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11118,19 +11122,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -11145,12 +11145,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -11195,12 +11195,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -11220,17 +11220,17 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11238,19 +11238,19 @@
       <c r="A114" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B114" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B114" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -11263,18 +11263,68 @@
       <c r="A115" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B115" s="16" t="inlineStr">
+      <c r="B115" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr"/>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="C117" s="7" t="inlineStr"/>
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -16079,7 +16129,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -17013,15 +17063,17 @@
       <c r="E45" s="20" t="n">
         <v>46311</v>
       </c>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F45" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>离线过 + 用户实转看过 (ffbfeeb); 未合</t>
+          <t>合主线 (task/d14-merge e215176; voxlive 冲突保留自动重连+网页按键); 回归 live_content ALL PASS + 重连 4/4 + live_push V1/V2</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -8528,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9998,101 +9998,101 @@
     </row>
     <row r="64">
       <c r="A64" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>半圈换帧: 换网格上限 1×→2×转速 (583 rpm 9.7→~19/s), 慢转均匀丢帧; 16/32 档位流时序收住 (REV 0x20471019/1A); 转速窗口 300-1200; 离线 16/16 + 仿真 21+5 + pls2047 32/32。主会话复验+上板假转扫点中</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d19-halfrev 1beafa6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+        <v>46310</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D20b</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>画面模拟器 host/pov_view.py (按视觉暂留合成人眼所见, 并排对比): 整圈换帧 9.8/s 跳 51 帧; 半圈 15/s 但 51/103 ms 交替 (内容 15 fps 与半圈节拍不齐 → D20 阶段 3 内容帧率跟转速); 300 rpm 闪烁; 停推冻结后跳帧。示例 gif 在 dr1v90/_work/d20b/d20_smooth/sim_out/; 复验 PASS</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 task/d20b-sim 9081f62</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B66" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46310</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>验证</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>半圈换帧上板假转扫点 PASS: 5/7.5/10/15/20 rps 换网格 9.00/13.56/15.09/15.09/15.08 每秒 (老行为 10 rps 仅 9.00), 完成率 100%, 撕裂 0, 对拍全一致, 超时 0; 卡上开机默认已是 D19 位流 0x20471019。D19+D20+D20b 合并分支全回归中</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 task/merge-d19-d20 106364e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46310</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D19/D20</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>半圈换帧 + 流畅度检测 + 画面模拟器合主线; 全回归 10 套 (D18/D13/D19/D20/D20b/color/pls2047/rotor_ops/live_push/重连) 通过; 下一步 D20 阶段 3 (内容帧率跟转速、主机侧停顿诊断) + 实转复核</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -10100,24 +10100,24 @@
       <c r="A68" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B68" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -10125,9 +10125,9 @@
       <c r="A69" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -10150,24 +10150,24 @@
       <c r="A70" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10175,24 +10175,24 @@
       <c r="A71" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10200,24 +10200,24 @@
       <c r="A72" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B72" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B72" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -10225,24 +10225,24 @@
       <c r="A73" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B73" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -10250,24 +10250,24 @@
       <c r="A74" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>交付完成</t>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10300,24 +10300,24 @@
       <c r="A76" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -10332,17 +10332,17 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -10350,24 +10350,24 @@
       <c r="A78" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10375,24 +10375,24 @@
       <c r="A79" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B79" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -10400,24 +10400,24 @@
       <c r="A80" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -10425,24 +10425,24 @@
       <c r="A81" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10457,17 +10457,17 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -10475,24 +10475,24 @@
       <c r="A83" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10500,24 +10500,24 @@
       <c r="A84" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B84" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -10525,30 +10525,30 @@
       <c r="A85" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B85" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
@@ -10557,73 +10557,73 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B88" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B89" s="18" t="inlineStr">
         <is>
@@ -10632,17 +10632,17 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -10652,22 +10652,22 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10675,24 +10675,24 @@
       <c r="A91" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10702,22 +10702,22 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10725,24 +10725,24 @@
       <c r="A93" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10750,24 +10750,24 @@
       <c r="A94" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10775,19 +10775,19 @@
       <c r="A95" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -10807,17 +10807,17 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10825,24 +10825,24 @@
       <c r="A97" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10850,24 +10850,24 @@
       <c r="A98" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10875,19 +10875,19 @@
       <c r="A99" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -10900,24 +10900,24 @@
       <c r="A100" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10925,24 +10925,24 @@
       <c r="A101" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10950,24 +10950,24 @@
       <c r="A102" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10975,24 +10975,24 @@
       <c r="A103" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11000,19 +11000,19 @@
       <c r="A104" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B104" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -11025,24 +11025,24 @@
       <c r="A105" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -11050,19 +11050,19 @@
       <c r="A106" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -11075,20 +11075,24 @@
       <c r="A107" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr"/>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -11096,20 +11100,24 @@
       <c r="A108" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr"/>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11117,20 +11125,24 @@
       <c r="A109" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B109" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr"/>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -11145,12 +11157,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D3;D4;D5</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11168,19 +11180,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11188,24 +11196,20 @@
       <c r="A112" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B112" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>D12;D13;D14</t>
-        </is>
-      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11218,19 +11222,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
+      <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -11245,12 +11245,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -11270,17 +11270,17 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11288,19 +11288,19 @@
       <c r="A116" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B116" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B116" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -11313,18 +11313,118 @@
       <c r="A117" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B117" s="16" t="inlineStr">
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B118" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>D15;D16</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr"/>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr"/>
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E121" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -8528,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10098,51 +10098,51 @@
     </row>
     <row r="68">
       <c r="A68" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>每圈片数随转速换档 (V1/V2 到 1200 rpm 的前提): N/PB/LUT 圈边界同步锁存, 回差 5%; V0 2047 人为 142/128 两档仿真逐字节一致、撕裂 0, 假转斜坡升降各 1 次不抖; 16/32 档位流时序收住 (REV 0x20471021/22)。风险: 软件写序时间窗 (可加影子寄存器)。主会话复验中, 诊断跑完后上板</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d21-nband adeba44</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+        <v>46310</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D20/D22</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>推流每 124.5 s 卡 3 s 的根因 = 长跑脚本的板上对拍 (--pl-verify 1800 ≈ 每 120 s, 每次停 ~3 s), 测试工具自身, 产品默认不开; WiFi 链路同刻 ping 0 丢。WSL/Windows 各 6 min 回放对照: 无周期卡顿, 但有偶发 1-1.7 s ACK 停顿 (每 6 min 1-2 次) = 真实 WiFi 抖动 → D22 WiFi 稳定 (用户 10-15: V0 必须搞定, 不能靠串口)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>~/realspin/tcp</t>
         </is>
       </c>
     </row>
@@ -10150,24 +10150,24 @@
       <c r="A70" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -10175,24 +10175,24 @@
       <c r="A71" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B71" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -10200,24 +10200,24 @@
       <c r="A72" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B72" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10232,17 +10232,17 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10250,24 +10250,24 @@
       <c r="A74" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B74" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -10275,9 +10275,9 @@
       <c r="A75" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -10300,24 +10300,24 @@
       <c r="A76" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B76" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -10325,24 +10325,24 @@
       <c r="A77" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B77" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10350,24 +10350,24 @@
       <c r="A78" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -10375,24 +10375,24 @@
       <c r="A79" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B79" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -10407,17 +10407,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10425,24 +10425,24 @@
       <c r="A81" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B81" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -10450,24 +10450,24 @@
       <c r="A82" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -10507,17 +10507,17 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -10525,24 +10525,24 @@
       <c r="A85" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10557,17 +10557,17 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -10577,22 +10577,22 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>开始</t>
+          <t>根因</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -10600,24 +10600,24 @@
       <c r="A88" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B88" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -10625,9 +10625,9 @@
       <c r="A89" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B89" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -10637,62 +10637,62 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B90" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B90" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -10707,17 +10707,17 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10725,24 +10725,24 @@
       <c r="A93" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10775,24 +10775,24 @@
       <c r="A95" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10807,17 +10807,17 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10825,24 +10825,24 @@
       <c r="A97" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10850,24 +10850,24 @@
       <c r="A98" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10875,9 +10875,9 @@
       <c r="A99" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10900,24 +10900,24 @@
       <c r="A100" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10925,19 +10925,19 @@
       <c r="A101" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -10957,17 +10957,17 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10975,19 +10975,19 @@
       <c r="A103" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -11000,24 +11000,24 @@
       <c r="A104" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -11025,24 +11025,24 @@
       <c r="A105" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B105" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -11075,24 +11075,24 @@
       <c r="A107" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -11100,9 +11100,9 @@
       <c r="A108" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -11125,24 +11125,24 @@
       <c r="A109" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B109" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -11150,19 +11150,19 @@
       <c r="A110" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B110" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11175,20 +11175,24 @@
       <c r="A111" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B111" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr"/>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -11196,20 +11200,24 @@
       <c r="A112" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr"/>
+      <c r="B112" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11225,12 +11233,12 @@
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11238,24 +11246,20 @@
       <c r="A114" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B114" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11268,19 +11272,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -11295,12 +11295,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -11370,17 +11370,17 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11388,19 +11388,19 @@
       <c r="A120" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B120" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B120" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -11413,18 +11413,68 @@
       <c r="A121" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B121" s="16" t="inlineStr">
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B122" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr"/>
-      <c r="D121" s="7" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr"/>
+      <c r="D123" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -8528,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10148,26 +10148,26 @@
     </row>
     <row r="70">
       <c r="A70" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B70" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>用户: 不插串口也必须永远连得上, 彻底解决 (V0 必须) → D22 四层兜底开做: 服务监护 + 硬件看门狗 + 兜底热点 + 故障注入验收</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>用户 10-15</t>
         </is>
       </c>
     </row>
@@ -10175,24 +10175,24 @@
       <c r="A71" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -10200,24 +10200,24 @@
       <c r="A72" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B72" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -10250,24 +10250,24 @@
       <c r="A74" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10275,24 +10275,24 @@
       <c r="A75" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B75" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -10300,9 +10300,9 @@
       <c r="A76" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -10325,9 +10325,9 @@
       <c r="A77" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -10350,24 +10350,24 @@
       <c r="A78" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10375,24 +10375,24 @@
       <c r="A79" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B79" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -10400,24 +10400,24 @@
       <c r="A80" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B80" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -10425,24 +10425,24 @@
       <c r="A81" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10450,9 +10450,9 @@
       <c r="A82" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B82" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -10475,24 +10475,24 @@
       <c r="A83" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B83" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -10500,9 +10500,9 @@
       <c r="A84" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10525,24 +10525,24 @@
       <c r="A85" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B85" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -10550,24 +10550,24 @@
       <c r="A86" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B86" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10575,24 +10575,24 @@
       <c r="A87" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
@@ -10600,24 +10600,24 @@
       <c r="A88" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -10625,24 +10625,24 @@
       <c r="A89" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
@@ -10650,24 +10650,24 @@
       <c r="A90" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B90" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -10675,49 +10675,49 @@
       <c r="A91" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B91" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B92" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -10732,17 +10732,17 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10757,17 +10757,17 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10775,9 +10775,9 @@
       <c r="A95" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10800,9 +10800,9 @@
       <c r="A96" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B96" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10825,24 +10825,24 @@
       <c r="A97" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10850,9 +10850,9 @@
       <c r="A98" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10882,17 +10882,17 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10900,9 +10900,9 @@
       <c r="A100" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -10950,24 +10950,24 @@
       <c r="A102" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10975,24 +10975,24 @@
       <c r="A103" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -11000,24 +11000,24 @@
       <c r="A104" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B104" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11032,17 +11032,17 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -11050,19 +11050,19 @@
       <c r="A106" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -11075,9 +11075,9 @@
       <c r="A107" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11100,24 +11100,24 @@
       <c r="A108" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -11125,9 +11125,9 @@
       <c r="A109" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11150,9 +11150,9 @@
       <c r="A110" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B110" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
@@ -11162,12 +11162,12 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -11175,24 +11175,24 @@
       <c r="A111" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B111" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11200,24 +11200,24 @@
       <c r="A112" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B112" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -11230,15 +11230,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr"/>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11246,15 +11250,15 @@
       <c r="A114" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B114" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -11267,20 +11271,20 @@
       <c r="A115" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B115" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11293,19 +11297,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -11320,12 +11320,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -11370,12 +11370,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -11420,17 +11420,17 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11438,24 +11438,24 @@
       <c r="A122" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B122" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B122" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -11463,18 +11463,43 @@
       <c r="A123" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B123" s="16" t="inlineStr">
+      <c r="B123" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr"/>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr"/>
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-15.xlsx
+++ b/docs/progress/显性目的进度_2026-10-15.xlsx
@@ -8528,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8631,16 +8631,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>33/45</t>
+          <t>34/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 16/24 + 交付 17/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 16/24 + 交付 18/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8663,16 +8663,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>31/49</t>
+          <t>32/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 14/24 + 交付 17/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 14/24 + 交付 18/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -8696,10 +8696,10 @@
         <v>0.973</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0.7333</v>
+        <v>0.7556</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.6327</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="8">
@@ -9070,7 +9070,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 4/11；状态由关联项在当日是否完成/达标推出)</t>
+          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 5/11；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
@@ -9215,9 +9215,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>⬜</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>D8 (0/1)</t>
+          <t>D8 (1/1)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -10173,126 +10173,126 @@
     </row>
     <row r="71">
       <c r="A71" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46310</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
+          <t>不插串口永远连得上: povreach 服务监护 + 硬件看门狗 (60 s, 防风暴) + 兜底热点 POV-&lt;板名&gt; (hostapd 静编, 192.168.77.1, 状态页可填 WiFi) + 30 min 无网重启; 失效模式表 16 行; 离线 9/9。排队上板故障演练 (8 项, 含 2 次看门狗复位)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 fdb4de6</t>
+          <t>dr1v90 task/d22-reach ee4a55c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+        <v>46310</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
+          <t>内容帧率跟转速 voxlive --fps auto: 583 rpm 换帧间隔 std 23.4→0.1-0.9 ms (离线假转)。取舍: 板端默认 (max-fps 15, margin 0.9) 下 583 rpm 均匀但仅 9.7 fps; 板端 max-fps 20 + margin 1.0 → 19.4 fps 均匀。计划 D22 后上板验证 20/1.0 后改开机默认</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>scratchpad/v_pls4_board.log</t>
+          <t>dr1v90 task/d20c-fps 338eaaf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B73" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46310</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>复验</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D20c</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>复验 F3 端到端节拍均匀度在主机忙 (D8 大仿真并行) 时不达标: 583 auto std 9.0/5.2 ms (门槛 3/4), 帧率正确; 主机计时抖动敏感, 先不合主线, 待空闲复验 + 上板实测定</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>~/rv_d20c.v.log</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B74" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46310</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>交付</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>V1 主控↔桥↔2260 联合仿真 0 错 (12/8 bit, 6 链×16 片, 训练锁定, 半圈换帧); 抓出并修 2 个回板必错 bug: 12-bit 字槽格式主控两 beat vs 桥紧排不一致 (改主控 PK12, 上行 195→110 µs/片) + 1 期切片器 NXG 未传 (160 宽按 192 算); 待: 1 期 12-bit 位流重综合 (hclk 余量原 +0.001 ns)</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 task/d8-cosim 85dfe51</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="20" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B75" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+        <v>46310</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>V1 联合仿真合主线 (新克隆复验 5/5; 合并回归 sim_v1/pls2047/D18/D19 通过, D19 O4 一次主机忙计时抖动重跑过); V1 回板就绪清单 ⑤ 达成</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>dr1v90 feature/lvds-b2b</t>
         </is>
       </c>
     </row>
@@ -10300,24 +10300,24 @@
       <c r="A76" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B76" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -10337,12 +10337,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -10350,24 +10350,24 @@
       <c r="A78" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10387,12 +10387,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -10407,17 +10407,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -10425,24 +10425,24 @@
       <c r="A81" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B81" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -10450,9 +10450,9 @@
       <c r="A82" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -10475,9 +10475,9 @@
       <c r="A83" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10500,24 +10500,24 @@
       <c r="A84" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B84" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -10525,24 +10525,24 @@
       <c r="A85" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -10550,24 +10550,24 @@
       <c r="A86" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B86" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -10582,17 +10582,17 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 dee9be6</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -10600,24 +10600,24 @@
       <c r="A88" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>根因</t>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D15b</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d15b-color-p2</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -10625,24 +10625,24 @@
       <c r="A89" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 3a41eb7</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -10650,24 +10650,24 @@
       <c r="A90" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>开始</t>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 26e69ec soak8h</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -10682,12 +10682,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -10700,55 +10700,55 @@
       <c r="A92" s="20" t="n">
         <v>46309</v>
       </c>
-      <c r="B92" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 5cbe79f</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B93" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
@@ -10757,92 +10757,92 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B96" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46309</v>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>用户批准 QoS 寄存器写入 + 网格 4×4 分块 (D16b 开做, 离线); 长跑后在 2047 做对照</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B97" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+        <v>46309</v>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>长跑第 6 段企业 WiFi 踢线 ~5 s, 推流端 voxlive 不重连直接退出 (板端处理正确); 修: voxlive 断线自动重连 5cbe79f; 23:45 重开 8 h</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 5cbe79f</t>
         </is>
       </c>
     </row>
@@ -10850,24 +10850,24 @@
       <c r="A98" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10877,22 +10877,22 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10902,22 +10902,22 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10932,17 +10932,17 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10950,24 +10950,24 @@
       <c r="A102" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10975,24 +10975,24 @@
       <c r="A103" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11000,24 +11000,24 @@
       <c r="A104" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -11032,17 +11032,17 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -11050,19 +11050,19 @@
       <c r="A106" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -11075,19 +11075,19 @@
       <c r="A107" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -11100,24 +11100,24 @@
       <c r="A108" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B108" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -11132,12 +11132,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -11150,24 +11150,24 @@
       <c r="A110" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -11175,19 +11175,19 @@
       <c r="A111" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B111" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -11200,24 +11200,24 @@
       <c r="A112" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B112" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11225,24 +11225,24 @@
       <c r="A113" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B113" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -11250,20 +11250,24 @@
       <c r="A114" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B114" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr"/>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>复验退回</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11276,15 +11280,19 @@
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr"/>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -11292,20 +11300,24 @@
       <c r="A116" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B116" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr"/>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11313,24 +11325,24 @@
       <c r="A117" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B117" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -11345,12 +11357,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3;D4;D5</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -11368,19 +11380,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>D12;D13;D14</t>
-        </is>
-      </c>
+      <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11388,24 +11396,20 @@
       <c r="A120" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B120" s="21" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -11418,19 +11422,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>D15;D16</t>
-        </is>
-      </c>
+      <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -11445,17 +11445,17 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -11463,19 +11463,19 @@
       <c r="A123" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B123" s="18" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
@@ -11488,18 +11488,143 @@
       <c r="A124" s="20" t="n">
         <v>46308</v>
       </c>
-      <c r="B124" s="16" t="inlineStr">
+      <c r="B124" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>D12;D13;D14</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B125" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B126" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>D15;D16</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr"/>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr"/>
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -16304,7 +16429,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -17020,15 +17145,17 @@
       <c r="E39" s="20" t="n">
         <v>46315</v>
       </c>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="26" t="inlineStr">
-        <is>
-          <t>⏸</t>
+      <c r="F39" s="20" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>待派 (D3+D4+D5 后)</t>
+          <t>合主线 68700ab (联合仿真 0 错; 修 12-bit 字槽格式 + 1 期 NXG); 待 1 期 12-bit 位流重综合</t>
         </is>
       </c>
     </row>
